--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.30845420332331</v>
+        <v>7.200123808040039</v>
       </c>
       <c r="D2" t="n">
-        <v>41.55384726138149</v>
+        <v>6.752500179974493</v>
       </c>
       <c r="E2" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F2" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.54228809686999</v>
+        <v>5.613121815741374</v>
       </c>
       <c r="D3" t="n">
-        <v>13.64327266050521</v>
+        <v>2.217031807332096</v>
       </c>
       <c r="E3" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.824442636595341</v>
+        <v>0.946471928446743</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460967539982662</v>
+        <v>1.049907225247183</v>
       </c>
       <c r="E4" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F4" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.71003393160863</v>
+        <v>7.265380513886402</v>
       </c>
       <c r="D5" t="n">
-        <v>12.80950591710227</v>
+        <v>2.081544711529118</v>
       </c>
       <c r="E5" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F5" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.59686266726888</v>
+        <v>11.95949018343119</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33015369585276</v>
+        <v>6.716149975576073</v>
       </c>
       <c r="E6" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F6" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>76.19738873778103</v>
+        <v>12.38207566988942</v>
       </c>
       <c r="D7" t="n">
-        <v>41.95598137024309</v>
+        <v>6.817846972664502</v>
       </c>
       <c r="E7" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F7" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.786642716205737</v>
+        <v>0.9403294413834323</v>
       </c>
       <c r="D8" t="n">
-        <v>5.485289209622539</v>
+        <v>0.8913594965636625</v>
       </c>
       <c r="E8" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F8" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.09525891220498</v>
+        <v>3.102979573233309</v>
       </c>
       <c r="D9" t="n">
-        <v>18.9700015217513</v>
+        <v>3.082625247284586</v>
       </c>
       <c r="E9" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F9" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.5837199017922</v>
+        <v>4.644854484041233</v>
       </c>
       <c r="D10" t="n">
-        <v>28.88715294353089</v>
+        <v>4.69416235332377</v>
       </c>
       <c r="E10" t="n">
-        <v>24.34075844074398</v>
+        <v>3.955373246620897</v>
       </c>
       <c r="F10" t="n">
-        <v>14.37707814195121</v>
+        <v>2.336275198067071</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
